--- a/Output/Means1950_table.xlsx
+++ b/Output/Means1950_table.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\altergc\Documents\Historical Demography\Handbook\DT_git\DemoTran\Output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7816385E-874C-4808-8E1B-C0387019A9CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{654A714B-BD97-44A4-A7D3-D787282FD28B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{FE127BF9-CED6-4A31-9076-3957202BE6AB}"/>
+    <workbookView xWindow="11184" yWindow="0" windowWidth="11520" windowHeight="12240" activeTab="2" xr2:uid="{FE127BF9-CED6-4A31-9076-3957202BE6AB}"/>
   </bookViews>
   <sheets>
     <sheet name="cdr-cbr-rni" sheetId="1" r:id="rId1"/>
@@ -124,7 +124,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -136,7 +136,6 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -196,7 +195,7 @@
             <v>Middle Africa</v>
           </cell>
           <cell r="D3" t="str">
-            <v>Angola, Cameroon, Central African Republic, Chad, Congo (Brazzaville), Congo (Kinshasa), Equatorial Guinea, Gabon, Sao Tome and Principe</v>
+            <v>Angola, Cameroon, Central African Republic, Chad, Congo_Brazzaville, Congo_Kinshasa, Equatorial Guinea, Gabon, Sao Tome and Principe</v>
           </cell>
         </row>
         <row r="4">
@@ -306,7 +305,7 @@
             <v>Western Asia</v>
           </cell>
           <cell r="D13" t="str">
-            <v>Armenia, Azerbaijan, Bahrain, Cyprus, Georgia, Iraq, Israel, Israel/Palestine Jews, Jordan, Kuwait, Lebanon, Oman, Qatar, Saudi Arabia, Syria, Turkey, United Arab Emirates, Yemen</v>
+            <v>Armenia, Azerbaijan, Bahrain, Cyprus, Georgia, Iraq, Israel, Jordan, Kuwait, Lebanon, Oman, Qatar, Saudi Arabia, Syria, Turkey, United Arab Emirates, Yemen</v>
           </cell>
         </row>
         <row r="14">
@@ -428,6 +427,17 @@
           </cell>
           <cell r="D24" t="str">
             <v>Bolivia, Brazil, Colombia, Ecuador, Guyana, Paraguay, Peru, Suriname, Venezuela</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="B25" t="str">
+            <v>South America</v>
+          </cell>
+          <cell r="C25" t="str">
+            <v>Southern Cone</v>
+          </cell>
+          <cell r="D25" t="str">
+            <v>Argentina, Chile, Uruguay</v>
           </cell>
         </row>
       </sheetData>
@@ -1193,13 +1203,13 @@
             <v>5.1258749999999997</v>
           </cell>
           <cell r="BP10">
-            <v>7.4249999999999998</v>
+            <v>7.4143749999999997</v>
           </cell>
           <cell r="BQ10">
-            <v>10.237857142857143</v>
+            <v>9.8343749999999996</v>
           </cell>
           <cell r="BR10">
-            <v>2.8128571428571427</v>
+            <v>2.42</v>
           </cell>
         </row>
         <row r="11">
@@ -1361,67 +1371,67 @@
             <v>Western Asia</v>
           </cell>
           <cell r="E13">
-            <v>20.514777777777777</v>
+            <v>21.315647058823529</v>
           </cell>
           <cell r="F13">
-            <v>42.522722222222221</v>
+            <v>43.006411764705881</v>
           </cell>
           <cell r="G13">
-            <v>22.007944444444444</v>
+            <v>21.690764705882355</v>
           </cell>
           <cell r="N13">
-            <v>15.452777777777778</v>
+            <v>16.026470588235295</v>
           </cell>
           <cell r="O13">
-            <v>42.094833333333334</v>
+            <v>42.988647058823531</v>
           </cell>
           <cell r="P13">
-            <v>26.642055555555554</v>
+            <v>26.962176470588236</v>
           </cell>
           <cell r="W13">
-            <v>10.836222222222222</v>
+            <v>11.061882352941176</v>
           </cell>
           <cell r="X13">
-            <v>37.695999999999998</v>
+            <v>38.331058823529411</v>
           </cell>
           <cell r="Y13">
-            <v>26.859777777777779</v>
+            <v>27.269176470588235</v>
           </cell>
           <cell r="AF13">
-            <v>7.8600555555555554</v>
+            <v>7.922411764705882</v>
           </cell>
           <cell r="AG13">
-            <v>33.839500000000001</v>
+            <v>34.40064705882353</v>
           </cell>
           <cell r="AH13">
-            <v>25.979444444444443</v>
+            <v>26.478235294117646</v>
           </cell>
           <cell r="AO13">
-            <v>6.2796111111111115</v>
+            <v>6.2842941176470593</v>
           </cell>
           <cell r="AP13">
-            <v>29.628722222222223</v>
+            <v>30.06570588235294</v>
           </cell>
           <cell r="AQ13">
-            <v>23.34911111111111</v>
+            <v>23.781411764705883</v>
           </cell>
           <cell r="AX13">
-            <v>5.1806111111111113</v>
+            <v>5.132411764705882</v>
           </cell>
           <cell r="AY13">
-            <v>22.377444444444446</v>
+            <v>22.41729411764706</v>
           </cell>
           <cell r="AZ13">
-            <v>17.196833333333334</v>
+            <v>17.284882352941178</v>
           </cell>
           <cell r="BG13">
-            <v>4.7650555555555556</v>
+            <v>4.7394705882352941</v>
           </cell>
           <cell r="BH13">
-            <v>20.424944444444446</v>
+            <v>20.344058823529412</v>
           </cell>
           <cell r="BI13">
-            <v>15.65988888888889</v>
+            <v>15.604588235294118</v>
           </cell>
           <cell r="BP13">
             <v>5.4565882352941175</v>
@@ -1515,13 +1525,13 @@
             <v>Northern Europe</v>
           </cell>
           <cell r="E15">
-            <v>11.502096104301712</v>
+            <v>11.50433139841936</v>
           </cell>
           <cell r="F15">
-            <v>19.723104471086899</v>
+            <v>19.726681277210417</v>
           </cell>
           <cell r="G15">
-            <v>8.2210083667851883</v>
+            <v>8.2223498787910589</v>
           </cell>
           <cell r="N15">
             <v>10.397477339045606</v>
@@ -4551,15 +4561,15 @@
       </c>
       <c r="W11" s="4">
         <f>[1]Means!BP10</f>
-        <v>7.4249999999999998</v>
+        <v>7.4143749999999997</v>
       </c>
       <c r="X11" s="4">
         <f>[1]Means!BQ10</f>
-        <v>10.237857142857143</v>
+        <v>9.8343749999999996</v>
       </c>
       <c r="Y11" s="4">
         <f>[1]Means!BR10</f>
-        <v>2.8128571428571427</v>
+        <v>2.42</v>
       </c>
       <c r="Z11" s="2">
         <f t="shared" si="2"/>
@@ -4611,11 +4621,11 @@
       </c>
       <c r="AR11" s="2">
         <f t="shared" si="14"/>
-        <v>0.72774999999999945</v>
+        <v>0.71712499999999935</v>
       </c>
       <c r="AS11" s="2">
         <f t="shared" si="15"/>
-        <v>-1.5852678571428562</v>
+        <v>-1.9887499999999996</v>
       </c>
       <c r="AU11" s="2">
         <f t="shared" si="16"/>
@@ -4643,11 +4653,11 @@
       </c>
       <c r="BA11" s="2">
         <f t="shared" si="22"/>
-        <v>-2.313017857142857</v>
+        <v>-2.7058749999999998</v>
       </c>
       <c r="BB11" s="2">
         <f t="shared" si="23"/>
-        <v>-22.012809523809523</v>
+        <v>-22.405666666666669</v>
       </c>
     </row>
     <row r="12" spans="1:54" x14ac:dyDescent="0.3">
@@ -5037,87 +5047,87 @@
       </c>
       <c r="B14" s="4">
         <f>[1]Means!E13</f>
-        <v>20.514777777777777</v>
+        <v>21.315647058823529</v>
       </c>
       <c r="C14" s="4">
         <f>[1]Means!F13</f>
-        <v>42.522722222222221</v>
+        <v>43.006411764705881</v>
       </c>
       <c r="D14" s="4">
         <f>[1]Means!G13</f>
-        <v>22.007944444444444</v>
+        <v>21.690764705882355</v>
       </c>
       <c r="E14" s="4">
         <f>[1]Means!N13</f>
-        <v>15.452777777777778</v>
+        <v>16.026470588235295</v>
       </c>
       <c r="F14" s="4">
         <f>[1]Means!O13</f>
-        <v>42.094833333333334</v>
+        <v>42.988647058823531</v>
       </c>
       <c r="G14" s="4">
         <f>[1]Means!P13</f>
-        <v>26.642055555555554</v>
+        <v>26.962176470588236</v>
       </c>
       <c r="H14" s="4">
         <f>[1]Means!W13</f>
-        <v>10.836222222222222</v>
+        <v>11.061882352941176</v>
       </c>
       <c r="I14" s="4">
         <f>[1]Means!X13</f>
-        <v>37.695999999999998</v>
+        <v>38.331058823529411</v>
       </c>
       <c r="J14" s="4">
         <f>[1]Means!Y13</f>
-        <v>26.859777777777779</v>
+        <v>27.269176470588235</v>
       </c>
       <c r="K14" s="4">
         <f>[1]Means!AF13</f>
-        <v>7.8600555555555554</v>
+        <v>7.922411764705882</v>
       </c>
       <c r="L14" s="4">
         <f>[1]Means!AG13</f>
-        <v>33.839500000000001</v>
+        <v>34.40064705882353</v>
       </c>
       <c r="M14" s="4">
         <f>[1]Means!AH13</f>
-        <v>25.979444444444443</v>
+        <v>26.478235294117646</v>
       </c>
       <c r="N14" s="4">
         <f>[1]Means!AO13</f>
-        <v>6.2796111111111115</v>
+        <v>6.2842941176470593</v>
       </c>
       <c r="O14" s="4">
         <f>[1]Means!AP13</f>
-        <v>29.628722222222223</v>
+        <v>30.06570588235294</v>
       </c>
       <c r="P14" s="4">
         <f>[1]Means!AQ13</f>
-        <v>23.34911111111111</v>
+        <v>23.781411764705883</v>
       </c>
       <c r="Q14" s="4">
         <f>[1]Means!AX13</f>
-        <v>5.1806111111111113</v>
+        <v>5.132411764705882</v>
       </c>
       <c r="R14" s="4">
         <f>[1]Means!AY13</f>
-        <v>22.377444444444446</v>
+        <v>22.41729411764706</v>
       </c>
       <c r="S14" s="4">
         <f>[1]Means!AZ13</f>
-        <v>17.196833333333334</v>
+        <v>17.284882352941178</v>
       </c>
       <c r="T14" s="4">
         <f>[1]Means!BG13</f>
-        <v>4.7650555555555556</v>
+        <v>4.7394705882352941</v>
       </c>
       <c r="U14" s="4">
         <f>[1]Means!BH13</f>
-        <v>20.424944444444446</v>
+        <v>20.344058823529412</v>
       </c>
       <c r="V14" s="4">
         <f>[1]Means!BI13</f>
-        <v>15.65988888888889</v>
+        <v>15.604588235294118</v>
       </c>
       <c r="W14" s="4">
         <f>[1]Means!BP13</f>
@@ -5133,91 +5143,91 @@
       </c>
       <c r="Z14" s="2">
         <f t="shared" si="2"/>
-        <v>-5.0619999999999994</v>
+        <v>-5.2891764705882345</v>
       </c>
       <c r="AA14" s="2">
         <f t="shared" si="3"/>
-        <v>-0.42788888888888721</v>
+        <v>-1.7764705882349574E-2</v>
       </c>
       <c r="AC14" s="2">
         <f t="shared" si="4"/>
-        <v>-4.6165555555555553</v>
+        <v>-4.9645882352941193</v>
       </c>
       <c r="AD14" s="2">
         <f t="shared" si="5"/>
-        <v>-4.3988333333333358</v>
+        <v>-4.6575882352941207</v>
       </c>
       <c r="AF14" s="2">
         <f t="shared" si="6"/>
-        <v>-2.9761666666666668</v>
+        <v>-3.1394705882352936</v>
       </c>
       <c r="AG14" s="2">
         <f t="shared" si="7"/>
-        <v>-3.8564999999999969</v>
+        <v>-3.9304117647058803</v>
       </c>
       <c r="AI14" s="2">
         <f t="shared" si="8"/>
-        <v>-1.5804444444444439</v>
+        <v>-1.6381176470588228</v>
       </c>
       <c r="AJ14" s="2">
         <f t="shared" si="9"/>
-        <v>-4.2107777777777784</v>
+        <v>-4.3349411764705899</v>
       </c>
       <c r="AL14" s="2">
         <f t="shared" si="10"/>
-        <v>-1.0990000000000002</v>
+        <v>-1.1518823529411772</v>
       </c>
       <c r="AM14" s="2">
         <f t="shared" si="11"/>
-        <v>-7.2512777777777764</v>
+        <v>-7.6484117647058802</v>
       </c>
       <c r="AO14" s="2">
         <f t="shared" si="12"/>
-        <v>-0.41555555555555568</v>
+        <v>-0.39294117647058791</v>
       </c>
       <c r="AP14" s="2">
         <f t="shared" si="13"/>
-        <v>-1.9525000000000006</v>
+        <v>-2.073235294117648</v>
       </c>
       <c r="AR14" s="2">
         <f t="shared" si="14"/>
-        <v>0.69153267973856192</v>
+        <v>0.71711764705882342</v>
       </c>
       <c r="AS14" s="2">
         <f t="shared" si="15"/>
-        <v>-3.5806503267973859</v>
+        <v>-3.4997647058823524</v>
       </c>
       <c r="AU14" s="2">
         <f t="shared" si="16"/>
-        <v>4.6341111111111104</v>
+        <v>5.2714117647058814</v>
       </c>
       <c r="AV14" s="2">
         <f t="shared" si="17"/>
-        <v>0.21772222222222481</v>
+        <v>0.30699999999999861</v>
       </c>
       <c r="AW14" s="2">
         <f t="shared" si="18"/>
-        <v>-0.8803333333333363</v>
+        <v>-0.79094117647058937</v>
       </c>
       <c r="AX14" s="2">
         <f t="shared" si="19"/>
-        <v>-2.6303333333333327</v>
+        <v>-2.6968235294117626</v>
       </c>
       <c r="AY14" s="2">
         <f t="shared" si="20"/>
-        <v>-6.1522777777777762</v>
+        <v>-6.4965294117647048</v>
       </c>
       <c r="AZ14" s="2">
         <f t="shared" si="21"/>
-        <v>-1.536944444444444</v>
+        <v>-1.68029411764706</v>
       </c>
       <c r="BA14" s="2">
         <f t="shared" si="22"/>
-        <v>-4.2721830065359487</v>
+        <v>-4.2168823529411767</v>
       </c>
       <c r="BB14" s="2">
         <f t="shared" si="23"/>
-        <v>-10.620238562091503</v>
+        <v>-10.303058823529414</v>
       </c>
     </row>
     <row r="15" spans="1:54" x14ac:dyDescent="0.3">
@@ -5417,15 +5427,15 @@
       </c>
       <c r="B16" s="4">
         <f>[1]Means!E15</f>
-        <v>11.502096104301712</v>
+        <v>11.50433139841936</v>
       </c>
       <c r="C16" s="4">
         <f>[1]Means!F15</f>
-        <v>19.723104471086899</v>
+        <v>19.726681277210417</v>
       </c>
       <c r="D16" s="4">
         <f>[1]Means!G15</f>
-        <v>8.2210083667851883</v>
+        <v>8.2223498787910589</v>
       </c>
       <c r="E16" s="4">
         <f>[1]Means!N15</f>
@@ -5513,11 +5523,11 @@
       </c>
       <c r="Z16" s="2">
         <f t="shared" si="2"/>
-        <v>-1.1046187652561059</v>
+        <v>-1.1068540593737541</v>
       </c>
       <c r="AA16" s="2">
         <f t="shared" si="3"/>
-        <v>-1.1581106226445748</v>
+        <v>-1.1616874287680936</v>
       </c>
       <c r="AC16" s="2">
         <f t="shared" si="4"/>
@@ -5569,7 +5579,7 @@
       </c>
       <c r="AU16" s="2">
         <f t="shared" si="16"/>
-        <v>-5.3491857388470621E-2</v>
+        <v>-5.4833369394341247E-2</v>
       </c>
       <c r="AV16" s="2">
         <f t="shared" si="17"/>
@@ -5597,7 +5607,7 @@
       </c>
       <c r="BB16" s="2">
         <f t="shared" si="23"/>
-        <v>-8.4181757514334556</v>
+        <v>-8.4195172634393263</v>
       </c>
     </row>
     <row r="17" spans="1:54" x14ac:dyDescent="0.3">
@@ -7786,7 +7796,7 @@
       </c>
       <c r="B6" s="2">
         <f>'cdr-cbr-rni'!AU16</f>
-        <v>-5.3491857388470621E-2</v>
+        <v>-5.4833369394341247E-2</v>
       </c>
       <c r="C6" s="2">
         <f>'cdr-cbr-rni'!AV16</f>
@@ -7814,7 +7824,7 @@
       </c>
       <c r="I6" s="2">
         <f>'cdr-cbr-rni'!BB16</f>
-        <v>-8.4181757514334556</v>
+        <v>-8.4195172634393263</v>
       </c>
       <c r="K6" s="2">
         <f>'cdr-cbr-rni'!Y16</f>
@@ -7978,15 +7988,15 @@
       </c>
       <c r="H10" s="2">
         <f>'cdr-cbr-rni'!BA11</f>
-        <v>-2.313017857142857</v>
+        <v>-2.7058749999999998</v>
       </c>
       <c r="I10" s="2">
         <f>'cdr-cbr-rni'!BB11</f>
-        <v>-22.012809523809523</v>
+        <v>-22.405666666666669</v>
       </c>
       <c r="K10" s="2">
         <f>'cdr-cbr-rni'!Y11</f>
-        <v>2.8128571428571427</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
@@ -8164,35 +8174,35 @@
       </c>
       <c r="B15" s="5">
         <f>'cdr-cbr-rni'!AU14</f>
-        <v>4.6341111111111104</v>
+        <v>5.2714117647058814</v>
       </c>
       <c r="C15" s="5">
         <f>'cdr-cbr-rni'!AV14</f>
-        <v>0.21772222222222481</v>
+        <v>0.30699999999999861</v>
       </c>
       <c r="D15" s="2">
         <f>'cdr-cbr-rni'!AW14</f>
-        <v>-0.8803333333333363</v>
+        <v>-0.79094117647058937</v>
       </c>
       <c r="E15" s="2">
         <f>'cdr-cbr-rni'!AX14</f>
-        <v>-2.6303333333333327</v>
+        <v>-2.6968235294117626</v>
       </c>
       <c r="F15" s="2">
         <f>'cdr-cbr-rni'!AY14</f>
-        <v>-6.1522777777777762</v>
+        <v>-6.4965294117647048</v>
       </c>
       <c r="G15" s="2">
         <f>'cdr-cbr-rni'!AZ14</f>
-        <v>-1.536944444444444</v>
+        <v>-1.68029411764706</v>
       </c>
       <c r="H15" s="2">
         <f>'cdr-cbr-rni'!BA14</f>
-        <v>-4.2721830065359487</v>
+        <v>-4.2168823529411767</v>
       </c>
       <c r="I15" s="2">
         <f>'cdr-cbr-rni'!BB14</f>
-        <v>-10.620238562091503</v>
+        <v>-10.303058823529414</v>
       </c>
       <c r="K15" s="2">
         <f>'cdr-cbr-rni'!Y14</f>
@@ -8629,7 +8639,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71592CD3-E34F-4178-9A61-B5C4ACABE806}">
-  <dimension ref="A1:K53"/>
+  <dimension ref="A1:K54"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="22.33203125" customWidth="1"/>
@@ -8676,7 +8686,7 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
-      <c r="B2" s="7" t="s">
+      <c r="B2" t="s">
         <v>10</v>
       </c>
       <c r="C2" s="1"/>
@@ -8894,15 +8904,15 @@
       </c>
       <c r="B9" s="2">
         <f>'cdr-cbr-rni'!B16</f>
-        <v>11.502096104301712</v>
+        <v>11.50433139841936</v>
       </c>
       <c r="C9" s="2">
         <f>'cdr-cbr-rni'!C16</f>
-        <v>19.723104471086899</v>
+        <v>19.726681277210417</v>
       </c>
       <c r="D9" s="2">
         <f>'cdr-cbr-rni'!D16</f>
-        <v>8.2210083667851883</v>
+        <v>8.2223498787910589</v>
       </c>
       <c r="E9" s="2">
         <f>'cdr-cbr-rni'!W16</f>
@@ -8918,15 +8928,15 @@
       </c>
       <c r="I9" s="2">
         <f t="shared" si="1"/>
-        <v>-1.3488945839053024</v>
+        <v>-1.3511298780229506</v>
       </c>
       <c r="J9" s="2">
         <f t="shared" si="0"/>
-        <v>-9.7670703353387562</v>
+        <v>-9.7706471414622751</v>
       </c>
       <c r="K9" s="2">
         <f t="shared" si="0"/>
-        <v>-8.4181757514334556</v>
+        <v>-8.4195172634393263</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
@@ -9074,27 +9084,27 @@
       </c>
       <c r="E13" s="2">
         <f>'cdr-cbr-rni'!W11</f>
-        <v>7.4249999999999998</v>
+        <v>7.4143749999999997</v>
       </c>
       <c r="F13" s="2">
         <f>'cdr-cbr-rni'!X11</f>
-        <v>10.237857142857143</v>
+        <v>9.8343749999999996</v>
       </c>
       <c r="G13" s="2">
         <f>'cdr-cbr-rni'!Y11</f>
-        <v>2.8128571428571427</v>
+        <v>2.42</v>
       </c>
       <c r="I13" s="2">
         <f t="shared" si="1"/>
-        <v>-7.8263333333333334</v>
+        <v>-7.8369583333333335</v>
       </c>
       <c r="J13" s="2">
         <f t="shared" si="0"/>
-        <v>-29.839142857142853</v>
+        <v>-30.242624999999997</v>
       </c>
       <c r="K13" s="2">
         <f t="shared" si="0"/>
-        <v>-22.012809523809523</v>
+        <v>-22.405666666666669</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
@@ -9272,15 +9282,15 @@
       </c>
       <c r="B18" s="2">
         <f>'cdr-cbr-rni'!B14</f>
-        <v>20.514777777777777</v>
+        <v>21.315647058823529</v>
       </c>
       <c r="C18" s="2">
         <f>'cdr-cbr-rni'!C14</f>
-        <v>42.522722222222221</v>
+        <v>43.006411764705881</v>
       </c>
       <c r="D18" s="2">
         <f>'cdr-cbr-rni'!D14</f>
-        <v>22.007944444444444</v>
+        <v>21.690764705882355</v>
       </c>
       <c r="E18" s="2">
         <f>'cdr-cbr-rni'!W14</f>
@@ -9296,15 +9306,15 @@
       </c>
       <c r="I18" s="2">
         <f t="shared" si="1"/>
-        <v>-15.05818954248366</v>
+        <v>-15.859058823529413</v>
       </c>
       <c r="J18" s="2">
         <f t="shared" si="0"/>
-        <v>-25.678428104575161</v>
+        <v>-26.162117647058821</v>
       </c>
       <c r="K18" s="2">
         <f t="shared" si="0"/>
-        <v>-10.620238562091503</v>
+        <v>-10.303058823529414</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
@@ -9766,7 +9776,7 @@
       </c>
       <c r="C32" t="str">
         <f>[1]Names!D3</f>
-        <v>Angola, Cameroon, Central African Republic, Chad, Congo (Brazzaville), Congo (Kinshasa), Equatorial Guinea, Gabon, Sao Tome and Principe</v>
+        <v>Angola, Cameroon, Central African Republic, Chad, Congo_Brazzaville, Congo_Kinshasa, Equatorial Guinea, Gabon, Sao Tome and Principe</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
@@ -9906,7 +9916,7 @@
       </c>
       <c r="C42" t="str">
         <f>[1]Names!D13</f>
-        <v>Armenia, Azerbaijan, Bahrain, Cyprus, Georgia, Iraq, Israel, Israel/Palestine Jews, Jordan, Kuwait, Lebanon, Oman, Qatar, Saudi Arabia, Syria, Turkey, United Arab Emirates, Yemen</v>
+        <v>Armenia, Azerbaijan, Bahrain, Cyprus, Georgia, Iraq, Israel, Jordan, Kuwait, Lebanon, Oman, Qatar, Saudi Arabia, Syria, Turkey, United Arab Emirates, Yemen</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
@@ -10061,6 +10071,20 @@
       <c r="C53" t="str">
         <f>[1]Names!D24</f>
         <v>Bolivia, Brazil, Colombia, Ecuador, Guyana, Paraguay, Peru, Suriname, Venezuela</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A54" t="str">
+        <f>[1]Names!B25</f>
+        <v>South America</v>
+      </c>
+      <c r="B54" t="str">
+        <f>[1]Names!C25</f>
+        <v>Southern Cone</v>
+      </c>
+      <c r="C54" t="str">
+        <f>[1]Names!D25</f>
+        <v>Argentina, Chile, Uruguay</v>
       </c>
     </row>
   </sheetData>
